--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_xgb_monthly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_xgb_monthly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -847,27 +848,27 @@
         <v>5.494242384343042</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="n">
@@ -958,27 +959,27 @@
         <v>1.295281120905988</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="n">
@@ -986,11 +987,11 @@
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF4" s="2" t="n">
@@ -998,7 +999,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH4" s="2" t="n">
@@ -1006,7 +1007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr"/>
@@ -1095,19 +1096,19 @@
         <v>3.328693267801384</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z5" s="2" t="n">
@@ -1115,7 +1116,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="n">
@@ -1123,19 +1124,19 @@
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH5" s="2" t="n">
@@ -1143,7 +1144,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr"/>
@@ -1236,27 +1237,27 @@
         <v>3.747002102796054</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="n">
@@ -1266,19 +1267,19 @@
         <v>0.05242476982353028</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH6" s="2" t="n">
@@ -1286,15 +1287,15 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AL6" s="2" t="n">
@@ -1302,15 +1303,15 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
     </row>
@@ -1393,19 +1394,19 @@
         <v>6.060631921300485</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X7" s="2" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z7" s="2" t="n">
@@ -1413,7 +1414,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="n">
@@ -1421,19 +1422,19 @@
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH7" s="2" t="n">
@@ -1441,7 +1442,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr"/>
@@ -1534,27 +1535,27 @@
         <v>5.435773657579668</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="n">
@@ -1564,19 +1565,19 @@
         <v>0.1125825953203092</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH8" s="2" t="n">
@@ -1584,15 +1585,15 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AL8" s="2" t="n">
@@ -1600,15 +1601,15 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AN8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -1691,11 +1692,11 @@
         <v>5.575851331579767</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X9" s="2" t="n">
@@ -1703,7 +1704,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n">
@@ -1711,7 +1712,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="n">
@@ -1719,11 +1720,11 @@
       </c>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF9" s="2" t="n">
@@ -1731,7 +1732,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH9" s="2" t="n">
@@ -1739,7 +1740,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr"/>
@@ -1832,27 +1833,27 @@
         <v>5.024257694702682</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X10" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB10" s="2" t="n">
@@ -1862,11 +1863,11 @@
         <v>0.1071091813699188</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF10" s="2" t="n">
@@ -1874,7 +1875,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH10" s="2" t="n">
@@ -1882,15 +1883,15 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ10" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AL10" s="2" t="n">
@@ -1898,15 +1899,15 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AN10" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/7</t>
         </is>
       </c>
     </row>
@@ -2151,28 +2152,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.09343144196767172</v>
+        <v>0.05644008609220919</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2715577666208222</v>
+        <v>0.08831268540851216</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1809616537571158</v>
+        <v>0.2970580221997946</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9994459833795014</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.4704588408798223</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -2181,10 +2182,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.7119888462278816</v>
+        <v>0.2724034021441992</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -2193,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1395291740668942</v>
+        <v>-0.08310591627222952</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -2239,49 +2240,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.1727422704228461</v>
+        <v>0.03522731644179133</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.2936057179925118</v>
+        <v>-0.02007948195991338</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3857020660410981</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1401986532528675</v>
+        <v>0.109751688353926</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1956510932256706</v>
+        <v>0.3134663783137708</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9722991689750693</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.368727712232564</v>
+        <v>-0.194516414529035</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.1921118441789917</v>
+        <v>-0.02985501211366604</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.7837618941180758</v>
+        <v>1.1460434676788</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3857020660410981</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.8577439452797431</v>
+        <v>0.2852245968941696</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.08513787889039803</v>
+        <v>0.01007636000372569</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.204715424720587</v>
+        <v>1.047066940607384</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1370443733149529</v>
+        <v>-0.07773805881689089</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -2333,58 +2334,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.3050913934539505</v>
+        <v>0.07488442474097812</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.4395948126489193</v>
+        <v>0.01745895379357942</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1109469294357623</v>
+        <v>0.07812037677756986</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1530752451527519</v>
+        <v>0.2757884445827267</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9518005540166204</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2627477773058103</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.3922472502781837</v>
+        <v>0.01671906081640784</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5584925916461387</v>
+        <v>0.918214415433338</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.770210184900723</v>
+        <v>0.2733293632849492</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.03400801284489896</v>
+        <v>0.0007277260805729213</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.081772824084672</v>
+        <v>1.003399227518678</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1175306843923517</v>
+        <v>-0.05422944133655971</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.1128543980796262</v>
+        <v>0.03830763318291619</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.167883078317224</v>
+        <v>0.04800733242104904</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.04711831283392454</v>
+        <v>-0.009255373448318727</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -2435,58 +2436,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.2151221026538714</v>
+        <v>-0.1442435408514305</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.3403532384701788</v>
+        <v>-0.1899621470120204</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1063946936086794</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.03579761655333651</v>
+        <v>0.1293756870739591</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.09369875321656458</v>
+        <v>0.2252504461886983</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.653185595567867</v>
+        <v>0.9888888888888889</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.03825894160069132</v>
+        <v>-0.194516414529035</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.9606765663423371</v>
+        <v>-0.02985501211366604</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.08132261162133095</v>
+        <v>1.1460434676788</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1063946936086794</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.1703459069473641</v>
+        <v>0.0624132813932019</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.3163822827899545</v>
+        <v>-0.1650342339521657</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.2392536173141715</v>
+        <v>0.2291207852101746</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.104859142573185</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.03613737928602578</v>
+        <v>-0.1733637187145392</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.644708569851226</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.370017644293207</v>
+        <v>-0.173363718714539</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -2541,67 +2542,67 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.1437720215384926</v>
+        <v>0.03106773189656087</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.2616497797155077</v>
+        <v>-0.02401684158871809</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3594525369392275</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.136218146491746</v>
+        <v>0.1056234016974804</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1614388363631765</v>
+        <v>0.2951756696586659</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9756232686980609</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3059822048459385</v>
+        <v>-0.194516414529035</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.3106021754893584</v>
+        <v>-0.02985501211366604</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.6503910188481313</v>
+        <v>1.1460434676788</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3594525369392275</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.6480442281520928</v>
+        <v>0.2800605133296381</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.03735107165953877</v>
+        <v>0.006017833002124551</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9101887362216873</v>
+        <v>1.028109455040453</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1175306843923517</v>
+        <v>-0.05422944133655982</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.0247029970821363</v>
+        <v>-0.004018039786206073</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.0993953141971935</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1128786976593124</v>
+        <v>-0.004018039786206073</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.1236077202903951</v>
+        <v>-0.04076409689811633</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.05864265472423225</v>
+        <v>-0.04580820280154452</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.06901211945940844</v>
+        <v>0.005286259972301144</v>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
@@ -2649,58 +2650,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.161667532662061</v>
+        <v>-0.07697127204873278</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.07526853881022866</v>
+        <v>-0.1262838848101959</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.5306006583632554</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.3273378511981809</v>
+        <v>0.1263742272469378</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1751333832746312</v>
+        <v>0.2383089143642949</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9977839335180055</v>
+        <v>0.9888888888888889</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.4528654141164017</v>
+        <v>-0.194516414529035</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.03322390802001429</v>
+        <v>-0.02985501211366604</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.9626036855200373</v>
+        <v>1.1460434676788</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.5044955376280438</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.5322234948537732</v>
+        <v>0.1459311457123906</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.105003809908105</v>
+        <v>-0.09939635198922214</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.7475166186570118</v>
+        <v>0.5357170452487251</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1370443733149529</v>
+        <v>-0.02110229120576934</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.2851519993087072</v>
+        <v>-0.1083806297501548</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>-0.1332827426678272</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1752235291914529</v>
+        <v>-0.1083806297501548</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -2755,67 +2756,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.005277165346246226</v>
+        <v>0.03163925839459969</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.1088815693411662</v>
+        <v>-0.02347584877183917</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.4447848555707743</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.2229752123557137</v>
+        <v>0.1058427954890121</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1858726414146026</v>
+        <v>0.2980741246617525</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9983379501385041</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.4235521165913714</v>
+        <v>-0.194516414529035</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.08857994035135142</v>
+        <v>-0.02985501211366604</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.9002957959069726</v>
+        <v>1.1460434676788</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.4447848555707743</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.7439168297433609</v>
+        <v>0.280770057891871</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.01864964458490959</v>
+        <v>0.00657547420383553</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.04484337596668</v>
+        <v>1.030714211650128</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1370443733149529</v>
+        <v>-0.05422944133655982</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.1427978757994443</v>
+        <v>-0.003465961523817063</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>-0.086847475203925</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.06127169238021213</v>
+        <v>-0.003465961523817063</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.2297266150183092</v>
+        <v>-0.04023238717669531</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.2181130613590055</v>
+        <v>-0.04580820280154452</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>-0.01485323911343139</v>
+        <v>0.005843495659069831</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -2863,67 +2864,67 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.3665311754515568</v>
+        <v>0.01633146664688923</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.5073666115418336</v>
+        <v>-0.03796582501302315</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1641897388021939</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.07456242612179807</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1050386702895408</v>
+        <v>0.0002468489756377671</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9174515235457064</v>
+        <v>0</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.05710516873404647</v>
+        <v>0.006089370624204005</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.7805883735884758</v>
+        <v>0.2117597153840092</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.1213818590957968</v>
+        <v>-0.03587709265072067</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1641897388021939</v>
+        <v>0</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.4492933147346017</v>
+        <v>0.01018010558677385</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1534446512733371</v>
+        <v>-0.2060850325577077</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.6310398219227149</v>
+        <v>0.03737143334716839</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1348931069116708</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.16524423986085</v>
+        <v>-0.01825285084231509</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.4936420456545065</v>
+        <v>0.24905012190403</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.2198637931685661</v>
+        <v>-0.2140050011274753</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="n">
-        <v>0.05726299061600626</v>
+        <v>0.09998223277219531</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>-0.04676350711538768</v>
+        <v>-0.0814831053233861</v>
       </c>
     </row>
     <row r="10">
@@ -2973,73 +2974,73 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.1377525814868692</v>
+        <v>0.07488442474097812</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.2550099729427158</v>
+        <v>0.01745895379357942</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.3885025197646095</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1471370214220752</v>
+        <v>0.07812037677756986</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1644597809803386</v>
+        <v>0.2757884445827267</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.978393351800554</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.3329360127594013</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.2597018678376435</v>
+        <v>0.01671906081640784</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.7076836140155546</v>
+        <v>0.918214415433338</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.3885025197646095</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.705612359907688</v>
+        <v>0.2733293632849492</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.00372460739697178</v>
+        <v>0.0007277260805729213</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.9910441204887179</v>
+        <v>1.003399227518678</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.1175306843923517</v>
+        <v>-0.05422944133655971</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.02983578729822789</v>
+        <v>0.03830763318291619</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.05669772009118912</v>
+        <v>0.04800733242104904</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.08189050259515007</v>
+        <v>-0.009255373448318727</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.1282199950182921</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.09520247385229641</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>-0.03649161299829362</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="2" t="n">
-        <v>0.05726299061600626</v>
+        <v>0.09998223277219531</v>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>-0.05537205093104502</v>
+        <v>-0.01738466379486436</v>
       </c>
     </row>
   </sheetData>
@@ -3283,28 +3284,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.05390587101818811</v>
+        <v>-0.09123360655355661</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2215345333965962</v>
+        <v>0.2716992530341495</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2389368129070568</v>
+        <v>0.1810585772249194</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9832848837209303</v>
+        <v>1</v>
       </c>
       <c r="P2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.503509252857314</v>
+        <v>-0.4707583434268612</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -3313,10 +3314,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>1.122709994261599</v>
+        <v>0.7171104771509156</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -3325,7 +3326,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1530343433756423</v>
+        <v>-0.1395291740668942</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -3371,49 +3372,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.03069342544864184</v>
+        <v>0.1701807858124662</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.08027215598020898</v>
+        <v>0.2876585162602945</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.6157753345140465</v>
+        <v>-0.385702066041098</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.2834217467647488</v>
+        <v>0.1402763471638039</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2902475246683776</v>
+        <v>0.1957580265743671</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0.9728230726566833</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.6131881355073265</v>
+        <v>-0.3701203966363428</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.2209082108402154</v>
+        <v>0.1901549992155818</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.217828931698091</v>
+        <v>0.78622163962527</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.6157753345140465</v>
+        <v>-0.385702066041098</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.50588635853417</v>
+        <v>0.8577848521582769</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.1805128186650207</v>
+        <v>0.08192505775212133</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.341295941276967</v>
+        <v>1.196168344334142</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1991621896471399</v>
+        <v>-0.1370443733149529</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -3465,58 +3466,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.2553938843122963</v>
+        <v>0.3109354176354568</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.1911821718000761</v>
+        <v>0.442543900268815</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.343246110573307</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1742196764528615</v>
+        <v>0.1110081735734261</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2118070551778035</v>
+        <v>0.1531549489989729</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9491279069767442</v>
+        <v>0.9517470881863561</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.4557974809248456</v>
+        <v>-0.2609524087912378</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.09609800828525117</v>
+        <v>0.3964274769943947</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.9052415190749453</v>
+        <v>0.5543234919463098</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.343246110573307</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.306850557115716</v>
+        <v>0.7738173200609908</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.08674786633685749</v>
+        <v>0.03302457451902874</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.164014361496109</v>
+        <v>1.079076857355887</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1243810385007439</v>
+        <v>-0.1175306843923517</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.2951463626390372</v>
+        <v>0.1202845180245065</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.4068920036589572</v>
+        <v>0.1733156420086164</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.07942730552828459</v>
+        <v>-0.04519766215110277</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -3567,68 +3568,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.08982278842242364</v>
+        <v>0.2122142938018965</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.03407981527755966</v>
+        <v>0.333911885984961</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1839140978547308</v>
+        <v>-0.1063946936086794</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.05250836017212767</v>
+        <v>0.0358100425160937</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.091676632705954</v>
+        <v>0.09374743802592535</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.3488372093023256</v>
+        <v>0.6533555185801442</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.02220992715952153</v>
+        <v>0.03596838162669824</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>1.058870045499055</v>
+        <v>0.9574581266611466</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.04411026616389797</v>
+        <v>-0.07640519202457094</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.1063946936086794</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.0661438120159743</v>
+        <v>0.170126729059485</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.4977440088857543</v>
+        <v>-0.3185489549857057</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.05891442345222619</v>
+        <v>0.2372392183355061</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1839140978547309</v>
+        <v>-0.104859142573185</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.124332401156823</v>
+        <v>0.03592052484458286</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>1.642654016055609</v>
+        <v>0.644708569851226</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.5745442292763747</v>
+        <v>-0.3701494940600397</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.1156075488991724</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.08239734478042915</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3677,74 +3674,70 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.1469945602555851</v>
+        <v>0.143574191546769</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.08832732770286511</v>
+        <v>0.2583808113874355</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.3594525369392275</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1773465422278632</v>
+        <v>0.1362936261161221</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2192507394803745</v>
+        <v>0.1615245012551946</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9709302325581395</v>
+        <v>0.9761508596783139</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.4557974809248456</v>
+        <v>-0.3075133155536084</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.09609800828525117</v>
+        <v>0.3084508293059751</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.9052415190749453</v>
+        <v>0.6532296662340193</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.3594525369392275</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>1.107661247516543</v>
+        <v>0.6514024272697743</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.007089403067653377</v>
+        <v>-0.03826664082218301</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9865960516767698</v>
+        <v>0.908371092077472</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1839140978547305</v>
+        <v>-0.1175306843923517</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.1833145367722999</v>
+        <v>-0.02273716556303229</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.4068920036589572</v>
+        <v>0.0993953141971935</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1589158700917991</v>
+        <v>-0.1110905951508532</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.08634686325247809</v>
+        <v>-0.1276655004031843</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0</v>
+        <v>-0.06300122930678531</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.08634686325247798</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.1156075488991724</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>0.005169824131459944</v>
-      </c>
+        <v>-0.06901211945940822</v>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3789,58 +3782,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.1099226210314619</v>
+        <v>-0.1634986048145926</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.05315156842152846</v>
+        <v>-0.07951988407821198</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.345107623352002</v>
+        <v>-0.5306006583632555</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1549993607170017</v>
+        <v>0.327487452117318</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1473471434925134</v>
+        <v>0.1752284186785477</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9760174418604651</v>
+        <v>0.9983361064891847</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.3068025924267069</v>
+        <v>-0.4540724777231742</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.3961940107900452</v>
+        <v>0.03152787672030333</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.6093286085323434</v>
+        <v>0.9645553479047804</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.345107623352002</v>
+        <v>-0.5044955376280438</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.601163837177374</v>
+        <v>0.5322572338846823</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2456982623599739</v>
+        <v>-0.1076536691878718</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.5354578121242757</v>
+        <v>0.7422248744703098</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1839140978547309</v>
+        <v>-0.1370443733149529</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.1450687018657515</v>
+        <v>-0.2851519993087072</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.7920789696625834</v>
+        <v>-0.1332827426678272</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.3610389267157421</v>
+        <v>-0.1752235291914528</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -3895,67 +3888,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.07568141012452956</v>
+        <v>0.003081455297121449</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.02066174950264199</v>
+        <v>0.1037836153832601</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.5035314930286399</v>
+        <v>-0.4447848555707743</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.2193324439759425</v>
+        <v>0.2230983505730857</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2309753169329724</v>
+        <v>0.1859739304225342</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9832848837209303</v>
+        <v>0.9988907376594565</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.5035314930286396</v>
+        <v>-0.424823849870926</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-4.479473475316187e-05</v>
+        <v>0.08679304243237929</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.000044170332917</v>
+        <v>0.9024244727739558</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.5035314930286399</v>
+        <v>-0.4447848555707743</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>1.16666595165639</v>
+        <v>0.7439552301882171</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.02070747182310262</v>
+        <v>0.01563367843509011</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.039151657702754</v>
+        <v>1.037434612786521</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1839140978547303</v>
+        <v>-0.1370443733149529</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.1097432312603541</v>
+        <v>-0.1427978757994444</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.2834883118761313</v>
+        <v>-0.08684747520392488</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.1353694295523477</v>
+        <v>-0.06127169238021213</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.1431522619581767</v>
+        <v>-0.2348353383369668</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.08771369192651968</v>
+        <v>-0.2217332726998885</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>-0.06076882831742725</v>
+        <v>-0.01683492969374489</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -4003,64 +3996,68 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.01319733068017759</v>
+        <v>0.3662506930886325</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.03862635312836959</v>
+        <v>0.5034124313369541</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.2571591117823077</v>
+        <v>-0.1641897388021938</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1496016882526679</v>
+        <v>0.07460374639256244</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1298179177095132</v>
+        <v>0.1050969169018788</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9949127906976745</v>
+        <v>0.9179145867997781</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.2066470204587323</v>
+        <v>-0.05731945666638372</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.5979209765882438</v>
+        <v>0.781191128146471</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.4104135510639614</v>
+        <v>0.1217598316986369</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.2169304194699831</v>
+        <v>-0.1641897388021938</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.2771078659917914</v>
+        <v>0.4493252276716546</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.3983597055442126</v>
+        <v>-0.1559510893693798</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.2468205212460443</v>
+        <v>0.6265774130881849</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1839140978547308</v>
+        <v>-0.1348931069116708</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.04528057198944935</v>
+        <v>0.1675552270669298</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>1.051004770967397</v>
+        <v>0.4966043324780678</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.490356830571183</v>
+        <v>-0.219863793168566</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.05960063366693302</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.04865028496396862</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4109,70 +4106,74 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.09404907951517161</v>
+        <v>0.1405483688679017</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.03808993725236665</v>
+        <v>0.2550512178849822</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.4970589048573092</v>
+        <v>-0.3885025197646093</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.2193757889837652</v>
+        <v>0.1472183876826421</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2252551997892281</v>
+        <v>0.164548351701009</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9781976744186046</v>
+        <v>0.978369384359401</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.4970589048573091</v>
+        <v>-0.3313115677688927</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.01299187958109349</v>
+        <v>0.2634841266292076</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.9871892165567953</v>
+        <v>0.7037826782997135</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.4970589048573092</v>
+        <v>-0.3885025197646093</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>1.175302615119919</v>
+        <v>0.705649916901379</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.02477616867141319</v>
+        <v>-0.006674328997486656</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>1.046844350836041</v>
+        <v>0.9840184175037165</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.1839140978547305</v>
+        <v>-0.1175306843923517</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0.1286925192079196</v>
+        <v>-0.02532293924480267</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.3002214805441084</v>
+        <v>0.06161309027980066</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.1319228792193223</v>
+        <v>-0.08189050259515007</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.1285212607878118</v>
+        <v>-0.129973640558803</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.0758199796696738</v>
+        <v>-0.09520247385229652</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>-0.057024908523018</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
+        <v>-0.03842977649878165</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0.05960063366693302</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>-0.05974576872210891</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4415,28 +4416,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.02340987064093203</v>
+        <v>0.05390587101818811</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.0812675747870259</v>
+        <v>0.2215345333965962</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2145128387962869</v>
+        <v>0.2389368129070568</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9832848837209303</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.1954368693665688</v>
+        <v>-0.503509252857314</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -4445,10 +4446,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2720069211165606</v>
+        <v>1.122709994261599</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -4457,7 +4458,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.03286068493604632</v>
+        <v>-0.1530343433756423</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -4503,49 +4504,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.03113418626728315</v>
+        <v>-0.03069342544864184</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.007547626662535167</v>
+        <v>-0.08027215598020898</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.05957889510636127</v>
+        <v>0.2834217467647488</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1870865456402408</v>
+        <v>0.2902475246683776</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9379310344827586</v>
+        <v>1</v>
       </c>
       <c r="P3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.6131881355073265</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.01865603812212591</v>
+        <v>-0.2209082108402154</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.9231979079208384</v>
+        <v>1.217828931698091</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2581357263948778</v>
+        <v>1.50588635853417</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.01090496796157892</v>
+        <v>0.1805128186650207</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.9490042581830531</v>
+        <v>1.341295941276967</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.0280449453540883</v>
+        <v>-0.1991621896471399</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -4597,58 +4598,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.0189637709832835</v>
+        <v>0.2553938843122963</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.004344397865602034</v>
+        <v>0.1911821718000761</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.04520489920804412</v>
+        <v>0.1742196764528615</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.165114162844639</v>
+        <v>0.2118070551778035</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9448275862068966</v>
+        <v>0.9491279069767442</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.4557974809248456</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.06570035000010499</v>
+        <v>0.09609800828525117</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7295286224594077</v>
+        <v>0.9052415190749453</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1884023656024003</v>
+        <v>1.306850557115716</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.06572649419295029</v>
+        <v>0.08674786633685749</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.6926381315189625</v>
+        <v>1.164014361496109</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1243810385007439</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.01180294034092366</v>
+        <v>0.2951463626390372</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.0461827251961362</v>
+        <v>0.4068920036589572</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.05542594437906534</v>
+        <v>-0.07942730552828459</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -4699,64 +4700,68 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.03113418626728315</v>
+        <v>0.08982278842242364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.007547626662535167</v>
+        <v>0.03407981527755966</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.1839140978547308</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.05957889510636127</v>
+        <v>0.05250836017212767</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1870865456402408</v>
+        <v>0.091676632705954</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9379310344827586</v>
+        <v>0.3488372093023256</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1804269089298145</v>
+        <v>0.02220992715952153</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.01865603812212591</v>
+        <v>1.058870045499055</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.9231979079208384</v>
+        <v>-0.04411026616389797</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1804269089298145</v>
+        <v>0</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2581357263948778</v>
+        <v>0.0661438120159743</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.01090496796157892</v>
+        <v>-0.4977440088857543</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.9490042581830531</v>
+        <v>0.05891442345222619</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.0280449453540883</v>
+        <v>-0.1839140978547309</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0</v>
+        <v>0.124332401156823</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0</v>
+        <v>1.642654016055609</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0</v>
+        <v>-0.5745442292763747</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.1156075488991724</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>-0.08239734478042915</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4805,70 +4810,74 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.03113418626728315</v>
+        <v>0.1469945602555851</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.007547626662535167</v>
+        <v>0.08832732770286511</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.05957889510636127</v>
+        <v>0.1773465422278632</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1870865456402408</v>
+        <v>0.2192507394803745</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9379310344827586</v>
+        <v>0.9709302325581395</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.4557974809248456</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.01865603812212591</v>
+        <v>0.09609800828525117</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.9231979079208384</v>
+        <v>0.9052415190749453</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2581357263948778</v>
+        <v>1.107661247516543</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.01090496796157892</v>
+        <v>-0.007089403067653377</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9490042581830531</v>
+        <v>0.9865960516767698</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.0280449453540883</v>
+        <v>-0.1839140978547305</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0</v>
+        <v>0.1833145367722999</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0</v>
+        <v>0.4068920036589572</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0</v>
+        <v>-0.1589158700917991</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.01194391364106639</v>
+        <v>-0.08634686325247809</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.04414403343113704</v>
+        <v>0</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.0586782413186544</v>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
+        <v>-0.08634686325247798</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>0.1156075488991724</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>0.005169824131459944</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4913,58 +4922,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.02507205106676125</v>
+        <v>0.1099226210314619</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.001624159072052267</v>
+        <v>0.05315156842152846</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.07305459408288872</v>
+        <v>-0.345107623352002</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.03295066899281222</v>
+        <v>0.1549993607170017</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.09826549443585531</v>
+        <v>0.1473471434925134</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9760174418604651</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.03628987298613628</v>
+        <v>-0.3068025924267069</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.1978054801680216</v>
+        <v>0.3961940107900452</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.1856859102571359</v>
+        <v>0.6093286085323434</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.07305459408288872</v>
+        <v>-0.345107623352002</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.0636725944169878</v>
+        <v>0.601163837177374</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.163783956864557</v>
+        <v>-0.2456982623599739</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.2340844643056078</v>
+        <v>0.5354578121242757</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.01683124201907893</v>
+        <v>-0.1839140978547309</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.005879094380981442</v>
+        <v>0.1450687018657515</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.1758684338397034</v>
+        <v>0.7920789696625834</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1545645099317813</v>
+        <v>-0.3610389267157421</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -5019,67 +5028,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.02185121148099589</v>
+        <v>0.07568141012452956</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.001523005791374654</v>
+        <v>0.02066174950264199</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1543024626822098</v>
+        <v>-0.5035314930286399</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.05289744897647698</v>
+        <v>0.2193324439759425</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1703919489317705</v>
+        <v>0.2309753169329724</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9586206896551724</v>
+        <v>0.9832848837209303</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1543024626822098</v>
+        <v>-0.5035314930286396</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.05112638787210377</v>
+        <v>-4.479473475316187e-05</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.7895258616366509</v>
+        <v>1.000044170332917</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1543024626822098</v>
+        <v>-0.5035314930286399</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.2082939424441199</v>
+        <v>1.16666595165639</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.050088547172773</v>
+        <v>0.02070747182310262</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7657670679447958</v>
+        <v>1.039151657702754</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1839140978547303</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.009002683559442226</v>
+        <v>0.1097432312603541</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.03187567592475715</v>
+        <v>0.2834883118761313</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.03961558590628134</v>
+        <v>-0.1353694295523477</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.002833702806652294</v>
+        <v>-0.1431522619581767</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.01367547841004246</v>
+        <v>-0.08771369192651968</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.01673808250258446</v>
+        <v>-0.06076882831742725</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -5127,58 +5136,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.0506491847673185</v>
+        <v>0.01319733068017759</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.02661623158796322</v>
+        <v>-0.03862635312836959</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.07305459408288872</v>
+        <v>-0.2571591117823077</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.03086354056037417</v>
+        <v>0.1496016882526679</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1042028394877494</v>
+        <v>0.1298179177095132</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.896551724137931</v>
+        <v>0.9949127906976745</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.03628987298613628</v>
+        <v>-0.2066470204587323</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1978054801680216</v>
+        <v>0.5979209765882438</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.1856859102571359</v>
+        <v>0.4104135510639614</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.07305459408288872</v>
+        <v>-0.2169304194699831</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.09021287139821044</v>
+        <v>0.2771078659917914</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1429190727663434</v>
+        <v>-0.3983597055442126</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.3316565292820339</v>
+        <v>0.2468205212460443</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.0191730400357899</v>
+        <v>-0.1839140978547308</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.01892576035198656</v>
+        <v>0.04528057198944935</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1758684338397034</v>
+        <v>1.051004770967397</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1334695863679521</v>
+        <v>-0.490356830571183</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -5233,67 +5242,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.03187250530379004</v>
+        <v>0.09404907951517161</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.008269057105691369</v>
+        <v>0.03808993725236665</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.1543024626822098</v>
+        <v>-0.4970589048573092</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.05189236258462471</v>
+        <v>0.2193757889837652</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1711769511511646</v>
+        <v>0.2252551997892281</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9379310344827586</v>
+        <v>0.9781976744186046</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.1543024626822098</v>
+        <v>-0.4970589048573091</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.05112638787210377</v>
+        <v>0.01299187958109349</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.7895258616366509</v>
+        <v>0.9871892165567953</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.1543024626822098</v>
+        <v>-0.4970589048573092</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.2201436799455174</v>
+        <v>1.175302615119919</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.0407727664921177</v>
+        <v>0.02477616867141319</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.809331170846132</v>
+        <v>1.046844350836041</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1839140978547305</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0.0007160261451319982</v>
+        <v>0.1286925192079196</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.03187567592475715</v>
+        <v>0.3002214805441084</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.03019709690481853</v>
+        <v>-0.1319228792193223</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.01266849194064057</v>
+        <v>-0.1285212607878118</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.01367547841004246</v>
+        <v>-0.0758199796696738</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.02670923187453211</v>
+        <v>-0.057024908523018</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -5539,28 +5548,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.09782647207714601</v>
+        <v>0.01891210187562598</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.2022979914860074</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1130717188570335</v>
+        <v>0.08099293800752018</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.459050197355985</v>
+        <v>0.2138559415886583</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9657534246575342</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2902196151348786</v>
+        <v>-0.1989728318606706</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -5569,10 +5578,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.2022979914860074</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5467128924473792</v>
+        <v>0.2720069211165606</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -5581,7 +5590,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.05185156587886086</v>
+        <v>-0.03286068493604632</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -5627,49 +5636,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.004064398596093755</v>
+        <v>0.02795562822442021</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.08540700726923578</v>
+        <v>0.008875668796304303</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.1829533120643722</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1330355594692814</v>
+        <v>0.06157120174811177</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4884782875332566</v>
+        <v>0.1864906684214894</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.952054794520548</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.1829533120643722</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.04551457597582553</v>
+        <v>0.01999872218255661</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.111313472861166</v>
+        <v>0.9194889088802032</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.1829533120643722</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.4820684921877625</v>
+        <v>0.2581357263948778</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.04179469931056778</v>
+        <v>-0.01090496796157892</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.8817580467688738</v>
+        <v>0.9490042581830531</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.09007578809896477</v>
+        <v>-0.0280449453540883</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -5721,58 +5730,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>-0.0009544101684616502</v>
+        <v>0.01970412365980478</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.08997859384708495</v>
+        <v>0.0007773210100467942</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1452798889626854</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1202708276706985</v>
+        <v>0.04505087866076889</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.428252010780779</v>
+        <v>0.1645456863596117</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0.9383561643835616</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1419538085967058</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.00807433626786469</v>
+        <v>0.07118238373413943</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>1.019747133566668</v>
+        <v>0.7134331218450367</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1452798889626854</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.4189993189650008</v>
+        <v>0.1884023656024003</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.08257096330288938</v>
+        <v>-0.06572649419295029</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7663973627717755</v>
+        <v>0.6926381315189625</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.07538615706116925</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.004998492897042128</v>
+        <v>-0.008027101888500976</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.03922557512728719</v>
+        <v>0.05018012320845067</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.04255483033018392</v>
+        <v>-0.05542594437906534</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -5823,58 +5832,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.2566500788127779</v>
+        <v>0.02795562822442021</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.3228894182331343</v>
+        <v>0.008875668796304303</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.1829533120643722</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.2432649587272604</v>
+        <v>0.06157120174811177</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4145143832447427</v>
+        <v>0.1864906684214894</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1</v>
+        <v>0.952054794520548</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.1829533120643722</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.04551457597582553</v>
+        <v>0.01999872218255661</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.111313472861166</v>
+        <v>0.9194889088802032</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.1829533120643722</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.09723589283939815</v>
+        <v>0.2581357263948778</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.290601443747436</v>
+        <v>-0.01090496796157892</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.1778554963357793</v>
+        <v>0.9490042581830531</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.05803403429873277</v>
+        <v>-0.0280449453540883</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.2596591192491325</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.2596591192491325</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -5929,67 +5938,67 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.03905582819587161</v>
+        <v>0.02795562822442021</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1246848238356186</v>
+        <v>0.008875668796304303</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.1829533120643722</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1488472589900897</v>
+        <v>0.06157120174811177</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4624555092660282</v>
+        <v>0.1864906684214894</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.952054794520548</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.1829533120643722</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.04551457597582553</v>
+        <v>0.01999872218255661</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.111313472861166</v>
+        <v>0.9194889088802032</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.1829533120643722</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.4184200553009263</v>
+        <v>0.2581357263948778</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.08294547603043112</v>
+        <v>-0.01090496796157892</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.7653378237119203</v>
+        <v>0.9490042581830531</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.07538615706116936</v>
+        <v>-0.0280449453540883</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.04294567843681851</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.04294567843681851</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.03813781714789888</v>
+        <v>0.008092057659824015</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.03774500557540916</v>
+        <v>-0.04778239665700701</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.0004082198323371866</v>
+        <v>0.0586782413186544</v>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
@@ -6037,68 +6046,64 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.04272888395753149</v>
+        <v>0.02191218006662776</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.0501878844434922</v>
+        <v>0.002944393520774913</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.09007578809896477</v>
+        <v>-0.07591198142831135</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.03642529566324065</v>
+        <v>0.03546326374903332</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1430561511166734</v>
+        <v>0.09801956934321687</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.4180327868852459</v>
+        <v>0.958904109589041</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.0007182735616988456</v>
+        <v>-0.0392605906832163</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.4098984628208118</v>
+        <v>0.1993842999713016</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.002474931135736743</v>
+        <v>0.1973163386984826</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0</v>
+        <v>-0.07591198142831135</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.04198045694350205</v>
+        <v>0.0636725944169878</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.3263258733850948</v>
+        <v>-0.163783956864557</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.07678702573772329</v>
+        <v>0.2340844643056078</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.09007578809896466</v>
+        <v>-0.01683124201907893</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.03850797360756864</v>
+        <v>-0.005879094380981442</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.4771293802231</v>
+        <v>0.1758684338397034</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.2969417658927641</v>
+        <v>-0.1545645099317813</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="n">
-        <v>0.02722714751693389</v>
-      </c>
-      <c r="AF7" s="2" t="n">
-        <v>-0.02590251273381827</v>
-      </c>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6147,74 +6152,70 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.01016957814200903</v>
+        <v>0.01870126899036806</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.07984585557431989</v>
+        <v>-0.0002069196006896368</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1569093966243399</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1196098851661267</v>
+        <v>0.05504738000015489</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.4369644818065765</v>
+        <v>0.1698566010913368</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9836065573770492</v>
+        <v>0.9657534246575342</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1569093966243399</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.00807433626786469</v>
+        <v>0.05251187089451403</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.019747133566668</v>
+        <v>0.7885970921608767</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1569093966243399</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.4347993304933977</v>
+        <v>0.2082939424441199</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.07235574391372634</v>
+        <v>-0.050088547172773</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7952973791179561</v>
+        <v>0.7657670679447958</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.09007578809896477</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.00608046610800228</v>
+        <v>-0.009002683559442337</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.03922557512728719</v>
+        <v>0.03187567592475715</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.03189404669455476</v>
+        <v>-0.03961558590628134</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.01113461530053539</v>
+        <v>-0.0009834761340744569</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>0</v>
+        <v>-0.01742981692299683</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.01113461530053539</v>
-      </c>
-      <c r="AE8" s="2" t="n">
-        <v>0.02722714751693389</v>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>-0.006765434017745875</v>
-      </c>
+        <v>0.01673808250258446</v>
+      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6259,58 +6260,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.04679020304884951</v>
+        <v>0.04741047009667154</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.1317299944975576</v>
+        <v>0.02796940792889346</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.133157003329941</v>
+        <v>-0.07591198142831135</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.0898938975842707</v>
+        <v>0.03316406506542453</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1237831084831679</v>
+        <v>0.1039405183346029</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1</v>
+        <v>0.9041095890410958</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.09214955767048905</v>
+        <v>-0.0392605906832163</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.2790582294015191</v>
+        <v>0.1993842999713016</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.3175166421045071</v>
+        <v>0.1973163386984826</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.133157003329941</v>
+        <v>-0.07591198142831135</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.04996346590441614</v>
+        <v>0.09021287139821044</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.3211645994344506</v>
+        <v>-0.1429190727663434</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.0913888561887629</v>
+        <v>0.3316565292820339</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.0009963797895713444</v>
+        <v>-0.0191730400357899</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.05064874495704597</v>
+        <v>0.01892576035198679</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.3400500386993066</v>
+        <v>0.1758684338397034</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.2915553691081392</v>
+        <v>-0.1334695863679521</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -6365,67 +6366,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.01045656418186702</v>
+        <v>0.02869167133026451</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.09863401822888795</v>
+        <v>0.009598050152349824</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.309428832058098</v>
+        <v>-0.1569093966243399</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1345705566556962</v>
+        <v>0.05397195999594626</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.4294414249717746</v>
+        <v>0.1706408739449248</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1</v>
+        <v>0.9452054794520548</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.309428832058098</v>
+        <v>-0.1569093966243399</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>-0.02706360633912097</v>
+        <v>0.05251187089451403</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1.066188554878663</v>
+        <v>0.7885970921608767</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.309428832058098</v>
+        <v>-0.1569093966243399</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.4329347672699009</v>
+        <v>0.2201436799455174</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.07356124445141599</v>
+        <v>-0.0407727664921177</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.7918868811230213</v>
+        <v>0.809331170846132</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.07538615706116925</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.01446218270288668</v>
+        <v>0.0007160261451319982</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.01933080293559009</v>
+        <v>0.03187567592475715</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.03315212837790826</v>
+        <v>-0.03019709690481853</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.009511231629587225</v>
+        <v>0.008813877929808367</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.01914384390439994</v>
+        <v>-0.01742981692299683</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.009820616626556644</v>
+        <v>0.02670923187453211</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -6671,28 +6672,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.06101703543393744</v>
+        <v>0.1113578145363066</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.3239608533428741</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1799741913752891</v>
+        <v>0.1112768582964018</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.240579627043532</v>
+        <v>0.4518304992174232</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9746588693957114</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.3098313187450097</v>
+        <v>-0.2902196151348786</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -6701,10 +6702,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.3098313187450098</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5373300241682992</v>
+        <v>0.5657770181230022</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -6713,7 +6714,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1055402030174765</v>
+        <v>-0.05185156587886086</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -6759,49 +6760,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.1265525925696835</v>
+        <v>-0.005339347390854843</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.06176673413065714</v>
+        <v>-0.1050041313434693</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3287615049188402</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1723102832459509</v>
+        <v>0.1309299660066359</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2353745170087453</v>
+        <v>0.4806983762937558</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9512670565302144</v>
+        <v>0.9920634920634921</v>
       </c>
       <c r="P3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.3283422830072888</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.0268209276442668</v>
+        <v>-0.04551457597582553</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.059745297335527</v>
+        <v>1.111313472861166</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3283422830072888</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.6772718664109521</v>
+        <v>0.4681879127595099</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.09102914796604056</v>
+        <v>-0.06232631098422858</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.260439275581632</v>
+        <v>0.8275131328464882</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1055180017892465</v>
+        <v>-0.09007578809896477</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -6853,58 +6854,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.05550959933794908</v>
+        <v>0.001402698831345583</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.005190714109256422</v>
+        <v>-0.09893763670599443</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1161134555088488</v>
+        <v>0.1183626651723915</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1734081721485486</v>
+        <v>0.4213989939818436</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9727095516569201</v>
+        <v>0.9920634920634921</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2377598766809244</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1044258367867865</v>
+        <v>-0.00807433626786469</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7673849036436503</v>
+        <v>1.019747133566668</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.3847468363930642</v>
+        <v>0.4223472503301919</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.09925207039248651</v>
+        <v>-0.09160293332491798</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7160345022383415</v>
+        <v>0.7464906434894674</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.07769789874505417</v>
+        <v>-0.07538615706116925</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.06306229615936909</v>
+        <v>0.006778237587377278</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1348639404188481</v>
+        <v>0.03922557512728719</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.1744052564619931</v>
+        <v>-0.03122261260355896</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -6955,68 +6956,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.01380564985556743</v>
+        <v>-0.2566378197499765</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.07051977752544158</v>
+        <v>-0.3311225506969799</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2944681800461371</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.178541669477491</v>
+        <v>0.2436974926820644</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1988154447477314</v>
+        <v>0.4078849916387119</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9590643274853801</v>
+        <v>1</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.2838263392633166</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.03767916480128619</v>
+        <v>-0.04551457597582553</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.9160672988546548</v>
+        <v>1.111313472861166</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2940275402431627</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.3770324213403713</v>
+        <v>0.09725398806391494</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.1042701308813958</v>
+        <v>-0.2992271726026072</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.7016775619861501</v>
+        <v>0.1718945537706014</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.0979033879303749</v>
+        <v>-0.05803403429873277</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.1245909364116696</v>
+        <v>-0.2526474448345049</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.06627772244364061</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.1790046390708484</v>
+        <v>-0.2526474448345047</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.7792202084776549</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.4371988460691945</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7065,74 +7062,70 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.03045119371441563</v>
+        <v>-0.03678861418809665</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.02880805934187558</v>
+        <v>-0.1333021883561547</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3157227764659216</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1781602597143876</v>
+        <v>0.1466573351320053</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2179960061656965</v>
+        <v>0.4550508760689094</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9883040935672515</v>
+        <v>1</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.315295411218274</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.007917039155309835</v>
+        <v>-0.04551457597582553</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.017635700920736</v>
+        <v>1.111313472861166</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.315295411218274</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.5049573357582811</v>
+        <v>0.4217666199741368</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.02105773509987352</v>
+        <v>-0.09197375902317173</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.939752690238879</v>
+        <v>0.7454643905002926</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.09790338793037456</v>
+        <v>-0.07538615706116936</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.08530573671315178</v>
+        <v>-0.03161808674621402</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.01942488183926638</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.102735003253463</v>
+        <v>-0.03161808674621402</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.02374057577425248</v>
+        <v>-0.03813781714789877</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.1017206155453103</v>
+        <v>-0.03774500557540916</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.08681045242777841</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.7792202084776549</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.05986522785946014</v>
-      </c>
+        <v>-0.0004082198323372976</v>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7177,67 +7170,67 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.3531645124263589</v>
+        <v>0.03296301876830521</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.2753466412279972</v>
+        <v>-0.07053965405436058</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1208274628418153</v>
+        <v>-0.09007578809896477</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.04616393688549093</v>
+        <v>0.03613062230870474</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1162633031291219</v>
+        <v>0.141130834766535</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9044834307992202</v>
+        <v>0.4365079365079365</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.05300588112757754</v>
+        <v>0.0007182735616988456</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.3721198086682598</v>
+        <v>0.4098984628208118</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.171079803495273</v>
+        <v>-0.002474931135736743</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1208274628418153</v>
+        <v>0</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.4289048743381425</v>
+        <v>0.03222160128228957</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.07052821978729984</v>
+        <v>-0.3407607920317542</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.7982149797082687</v>
+        <v>0.05695106066553673</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.09790338793037467</v>
+        <v>-0.09007578809896466</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.2011552069129503</v>
+        <v>0.03850797360756864</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.409935589086218</v>
+        <v>0.4771293802231</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1480779574537719</v>
+        <v>-0.2969417658927641</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
       <c r="AE7" s="2" t="n">
-        <v>0.06155864235340314</v>
+        <v>0.02722714751693389</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>-0.05888323104964921</v>
+        <v>-0.02590251273381827</v>
       </c>
     </row>
     <row r="8">
@@ -7287,73 +7280,73 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.1937077246096734</v>
+        <v>0.0007086529962982979</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.1250599045485332</v>
+        <v>-0.0995621392973014</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.2528925789158353</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.123919586857743</v>
+        <v>0.1177181088761107</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1934484639182608</v>
+        <v>0.4300293698285791</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9337231968810916</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.2528925789158352</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.08249974444745622</v>
+        <v>-0.00807433626786469</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.8162266485524824</v>
+        <v>1.019747133566668</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.2528925789158353</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.5977725437092092</v>
+        <v>0.4213614589135772</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.03931655440972048</v>
+        <v>-0.09223251940595301</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.11248677129938</v>
+        <v>0.7447482761167432</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.09790338793037467</v>
+        <v>-0.09007578809896477</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.05961118236549257</v>
+        <v>0.006080466108002058</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1123335624420028</v>
+        <v>0.03922557512728719</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.04739799450154525</v>
+        <v>-0.03189404669455476</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.1309302401024177</v>
+        <v>-0.0006930736614323418</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.01985293317939951</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.1538372948163047</v>
+        <v>-0.0006930736614324529</v>
       </c>
       <c r="AE8" s="2" t="n">
-        <v>0.06155864235340314</v>
+        <v>0.02722714751693389</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.001367825774972298</v>
+        <v>-0.006765434017745875</v>
       </c>
     </row>
     <row r="9">
@@ -7399,68 +7392,64 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.3543656143716478</v>
+        <v>-0.05571766110366438</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.2764786701259099</v>
+        <v>-0.1503345488326638</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.09928531078041158</v>
+        <v>-0.133157003329941</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.04747954682294232</v>
+        <v>0.08897480619140022</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1133818301410195</v>
+        <v>0.1221185311539384</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.6101364522417154</v>
+        <v>1</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.03921997818262724</v>
+        <v>-0.09214955767048905</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.3920944950302696</v>
+        <v>0.2790582294015191</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.1265849377057494</v>
+        <v>0.3175166421045071</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.09810919276948094</v>
+        <v>-0.133157003329941</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.4096521405698925</v>
+        <v>0.04012984393480257</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.08305170756518654</v>
+        <v>-0.3357101094882123</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.7623846093543133</v>
+        <v>0.07092872748337434</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.09790338793037479</v>
+        <v>-0.009365680129777787</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.2022213816776359</v>
+        <v>-0.05064874495704597</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.4304607801116043</v>
+        <v>0.3400500386993066</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1595565580037515</v>
+        <v>-0.2915553691081392</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="n">
-        <v>0.06155864235340314</v>
-      </c>
-      <c r="AF9" s="2" t="n">
-        <v>-0.05794117449794767</v>
-      </c>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7509,74 +7498,70 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.2259960485270862</v>
+        <v>-0.01972431147626086</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.15549138947206</v>
+        <v>-0.117947725114309</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.2460561291388812</v>
+        <v>-0.309428832058098</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1143652424362713</v>
+        <v>0.1324706378159778</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1910495833804597</v>
+        <v>0.4226222983105438</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9298245614035088</v>
+        <v>1</v>
       </c>
       <c r="P10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.2460561291388812</v>
+        <v>-0.309428832058098</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.09240522112675542</v>
+        <v>-0.02706360633912097</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.7941615784212722</v>
+        <v>1.066188554878663</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.2460561291388812</v>
+        <v>-0.309428832058098</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.6261105049196989</v>
+        <v>0.4195143585928134</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.05774978654920249</v>
+        <v>-0.09341218949906627</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>1.165225237299586</v>
+        <v>0.7414835618183581</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.09790338793037467</v>
+        <v>-0.07538615706116925</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0.08827235995309435</v>
+        <v>-0.01446218270288679</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.1225120352027469</v>
+        <v>0.01933080293559009</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.03050272440372404</v>
+        <v>-0.03315212837790826</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.1615205103734461</v>
+        <v>-0.02109741698545653</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.01088404061154891</v>
+        <v>-0.01914384390439994</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.1743016573017271</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>0.06155864235340314</v>
-      </c>
-      <c r="AF10" s="2" t="n">
-        <v>0.001697815565633309</v>
-      </c>
+        <v>-0.001991701911555621</v>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7819,28 +7804,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.002396027003975565</v>
+        <v>0.06101703543393744</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3239608533428741</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1038210158252798</v>
+        <v>0.1799741913752891</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3353086213004998</v>
+        <v>0.240579627043532</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1</v>
+        <v>0.9746588693957114</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3098313187450097</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -7849,10 +7834,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3098313187450098</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2859055823922789</v>
+        <v>0.5373300241682992</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -7861,7 +7846,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.07899825662835758</v>
+        <v>-0.1055402030174765</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -7907,49 +7892,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.01500324256968033</v>
+        <v>0.1265525925696835</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.01263749534581593</v>
+        <v>0.06176673413065714</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1891226670882522</v>
+        <v>-0.3287615049188402</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.09328475897205027</v>
+        <v>0.1723102832459509</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.3054222199740849</v>
+        <v>0.2353745170087453</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0.9512670565302144</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1891226670882522</v>
+        <v>-0.3283422830072888</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.04521605491915381</v>
+        <v>-0.0268209276442668</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.8435398396664642</v>
+        <v>1.059745297335527</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1891226670882522</v>
+        <v>-0.3283422830072888</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.214729672974497</v>
+        <v>0.6772718664109521</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.05535080521648206</v>
+        <v>0.09102914796604056</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.7510509979475514</v>
+        <v>1.260439275581632</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.08996647052893747</v>
+        <v>-0.1055180017892465</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -8001,58 +7986,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>-0.04941120899711726</v>
+        <v>0.05550959933794908</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.04712810219865582</v>
+        <v>-0.005190714109256422</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.07294179359961758</v>
+        <v>0.1161134555088488</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2326154609655196</v>
+        <v>0.1734081721485486</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0.9727095516569201</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.2377598766809244</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.09388774724005255</v>
+        <v>0.1044258367867865</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.6751222101795875</v>
+        <v>0.7673849036436503</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1201362258412626</v>
+        <v>0.3847468363930642</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1289125413411937</v>
+        <v>-0.09925207039248651</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.4201954534641747</v>
+        <v>0.7160345022383415</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.07769789874505417</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.03493206060617005</v>
+        <v>-0.06306229615936909</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.04656615452071611</v>
+        <v>0.1348639404188481</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.07787201485051753</v>
+        <v>-0.1744052564619931</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -8103,67 +8088,67 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.01380564985556743</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.01733422320252243</v>
+        <v>-0.07051977752544158</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>-0.2944681800461371</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>0.178541669477491</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.1988154447477314</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0</v>
+        <v>0.9590643274853801</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.2838263392633166</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.2963414873615395</v>
+        <v>0.03767916480128619</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.02542419299884719</v>
+        <v>0.9160672988546548</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.2940275402431627</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.3770324213403713</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2152266720452529</v>
+        <v>-0.1042701308813958</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.03198399714010954</v>
+        <v>0.7016775619861501</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0</v>
+        <v>-0.0979033879303749</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.03035533393972223</v>
+        <v>-0.1245909364116696</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.2402617442207293</v>
+        <v>0.06627772244364061</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.1692436384973673</v>
+        <v>-0.1790046390708484</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="n">
-        <v>0.1818988367474383</v>
+        <v>0.7792202084776549</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.1368328282013731</v>
+        <v>-0.4371988460691945</v>
       </c>
     </row>
     <row r="6">
@@ -8213,73 +8198,73 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.04941120899711726</v>
+        <v>0.03045119371441563</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.04712810219865582</v>
+        <v>-0.02880805934187558</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.3157227764659216</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.07294179359961758</v>
+        <v>0.1781602597143876</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2326154609655196</v>
+        <v>0.2179960061656965</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.9883040935672515</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.315295411218274</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.09388774724005255</v>
+        <v>-0.007917039155309835</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.6751222101795875</v>
+        <v>1.017635700920736</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.315295411218274</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.1201362258412626</v>
+        <v>0.5049573357582811</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1289125413411937</v>
+        <v>-0.02105773509987352</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.4201954534641747</v>
+        <v>0.939752690238879</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.09790338793037456</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.03493206060617005</v>
+        <v>-0.08530573671315178</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.04656615452071611</v>
+        <v>0.01942488183926638</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.07787201485051753</v>
+        <v>-0.102735003253463</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0</v>
+        <v>-0.02374057577425248</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0</v>
+        <v>-0.1017206155453103</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0</v>
+        <v>0.08681045242777841</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>0.1818988367474383</v>
+        <v>0.7792202084776549</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>-0.05128610654981658</v>
+        <v>-0.05986522785946014</v>
       </c>
     </row>
     <row r="7">
@@ -8325,64 +8310,68 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.06063956413672589</v>
+        <v>0.3531645124263589</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.06318698887233953</v>
+        <v>0.2753466412279972</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.05069935962761241</v>
+        <v>-0.1208274628418153</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.03366555804190518</v>
+        <v>0.04616393688549093</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1257220298601265</v>
+        <v>0.1162633031291219</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.8409090909090909</v>
+        <v>0.9044834307992202</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.04232177951775717</v>
+        <v>-0.05300588112757754</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.2344415250825462</v>
+        <v>0.3721198086682598</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.1887669397775003</v>
+        <v>0.171079803495273</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.05069935962761241</v>
+        <v>-0.1208274628418153</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.1075114181907955</v>
+        <v>0.4289048743381425</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1387303754211889</v>
+        <v>-0.07052821978729984</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.3760381916687573</v>
+        <v>0.7982149797082687</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.02753021075048012</v>
+        <v>-0.09790338793037467</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.07679498042586941</v>
+        <v>0.2011552069129503</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.1810395748064055</v>
+        <v>0.409935589086218</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.08826511541547943</v>
+        <v>-0.1480779574537719</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="inlineStr"/>
-      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="n">
+        <v>0.06155864235340314</v>
+      </c>
+      <c r="AF7" s="2" t="n">
+        <v>-0.05888323104964921</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8431,70 +8420,74 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.001296653643044543</v>
+        <v>0.1937077246096734</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.003701549659961945</v>
+        <v>0.1250599045485332</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1655864927329398</v>
+        <v>-0.2528925789158353</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.07789842917453209</v>
+        <v>0.123919586857743</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.245504062631617</v>
+        <v>0.1934484639182608</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9886363636363636</v>
+        <v>0.9337231968810916</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1655864927329398</v>
+        <v>-0.2528925789158352</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.07555404355081596</v>
+        <v>0.08249974444745622</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.7385619380340933</v>
+        <v>0.8162266485524824</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1655864927329398</v>
+        <v>-0.2528925789158353</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.2000005332159278</v>
+        <v>0.5977725437092092</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.06680509856449546</v>
+        <v>0.03931655440972048</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.6995335017331545</v>
+        <v>1.11248677129938</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.09790338793037467</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.01654817245820017</v>
+        <v>0.05961118236549257</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.02902556700012471</v>
+        <v>0.1123335624420028</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.01212544657981562</v>
+        <v>-0.04739799450154525</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.0533436361969557</v>
+        <v>0.1309302401024177</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.01676013259632336</v>
+        <v>-0.01985293317939951</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.0712987452170688</v>
-      </c>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
+        <v>0.1538372948163047</v>
+      </c>
+      <c r="AE8" s="2" t="n">
+        <v>0.06155864235340314</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>0.001367825774972298</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8539,64 +8532,68 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.06742087145063913</v>
+        <v>0.3543656143716478</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.06518101993056391</v>
+        <v>0.2764786701259099</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1262973638890311</v>
+        <v>-0.09928531078041158</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.09370441674274725</v>
+        <v>0.04747954682294232</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.15159769683826</v>
+        <v>0.1133818301410195</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1</v>
+        <v>0.6101364522417154</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1034054819434311</v>
+        <v>-0.03921997818262724</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1557049962909995</v>
+        <v>0.3920944950302696</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.4612172882401871</v>
+        <v>0.1265849377057494</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1262973638890311</v>
+        <v>-0.09810919276948094</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.04013476523455783</v>
+        <v>0.4096521405698925</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1911266429845438</v>
+        <v>-0.08305170756518654</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.1403776900707403</v>
+        <v>0.7623846093543133</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.01906855625568105</v>
+        <v>-0.09790338793037479</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.053216042068714</v>
+        <v>0.2022213816776359</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1057091888819022</v>
+        <v>0.4304607801116043</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.143731491560925</v>
+        <v>-0.1595565580037515</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.06155864235340314</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.05794117449794767</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8645,70 +8642,74 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.05717862820657083</v>
+        <v>0.2259960485270862</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.05491417705371704</v>
+        <v>0.15549138947206</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.1821196302820544</v>
+        <v>-0.2460561291388812</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1008800822003308</v>
+        <v>0.1143652424362713</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2527376754938562</v>
+        <v>0.1910495833804597</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1</v>
+        <v>0.9298245614035088</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.1821196302820544</v>
+        <v>-0.2460561291388812</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.05424292767282157</v>
+        <v>0.09240522112675542</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.8123043424326933</v>
+        <v>0.7941615784212722</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.1821196302820544</v>
+        <v>-0.2460561291388812</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.1527619523605521</v>
+        <v>0.6261105049196989</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.1035407512455374</v>
+        <v>0.05774978654920249</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.5343090928212585</v>
+        <v>1.165225237299586</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.09790338793037467</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.042817791346764</v>
+        <v>0.08827235995309435</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.008636370165942209</v>
+        <v>0.1225120352027469</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.05101358927225763</v>
+        <v>-0.03050272440372404</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.008171166421243825</v>
+        <v>0.1615205103734461</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.03624212783007885</v>
+        <v>-0.01088404061154891</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.02912657029263244</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
+        <v>0.1743016573017271</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0.06155864235340314</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>0.001697815565633309</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8721,7 +8722,1139 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AF10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>full_cum_return</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>full_excess_return</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>full_max_dd</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_ann_vol</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_underwater_share</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_recovered</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_cum_return</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_excess_return</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_down_capture</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cum_return</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_excess_return</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_recovery_capture</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_max_dd</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>0.004925019651871976</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.1032426212645823</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.3336266559947869</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.9887640449438202</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>0.2953423679490121</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>-0.07899825662835758</v>
+      </c>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>-0.01015087478268217</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>-0.0150020092442088</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>-0.1891226670882522</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.09277123339370263</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.3038024735945229</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>-0.1891226670882522</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.04521605491915381</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0.8435398396664642</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>-0.1891226670882522</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0.220713768953076</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>-0.05761303022466546</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>0.7473149568272576</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>-0.08996647052893747</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
+        <v>-0.04521242326464603</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>-0.04989172518949392</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0.07269182521527755</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.2314419517208828</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.09388774724005255</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>0.6751222101795875</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0.1250839088436306</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>-0.1314389641828525</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>0.4235217239987224</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>-0.0354211036699823</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.04656615452071611</v>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>-0.07833929832008091</v>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.0100920662696089</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.2963414873615395</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>-0.02542419299884719</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>-0.2208132840633974</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>0.03153481080418825</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>0.02547627076331693</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.2402617442207293</v>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>-0.173177536482321</v>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.1818988367474383</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>-0.1368328282013731</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>-0.04521242326464603</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>-0.04989172518949392</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0.07269182521527755</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.2314419517208828</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.09388774724005255</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0.6751222101795875</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0.1250839088436306</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>-0.1314389641828525</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0.4235217239987224</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>-0.0354211036699823</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.04656615452071611</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>-0.07833929832008091</v>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>0.1818988367474383</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>-0.05128610654981658</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.06586456941294583</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.06064089217540292</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>-0.05069935962761241</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0.03347800472719811</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.1252095931167156</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.8314606741573034</v>
+      </c>
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>-0.04232177951775717</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.2344415250825462</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>0.1887669397775003</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>-0.05069935962761241</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0.1129673272471681</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>-0.1407929248779292</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0.3824961790333811</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>-0.02753021075048012</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>0.07679498042586963</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.1810395748064055</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>-0.08826511541547932</v>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.006229319249012599</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.001297907377798557</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.1655864927329398</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0.07746445126203257</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0.2442443474035323</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.9775280898876404</v>
+      </c>
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>-0.1655864927329398</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0.07555404355081596</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>0.7385619380340933</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>-0.1655864927329398</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0.2059120693583902</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>-0.06903989308419045</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0.6971978683191802</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>0.01654817245820017</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.02902556700012471</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>-0.01212544657981551</v>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>0.05387768312774899</v>
+      </c>
+      <c r="AC8" s="2" t="n">
+        <v>-0.01676013259632336</v>
+      </c>
+      <c r="AD8" s="2" t="n">
+        <v>0.0718418954172364</v>
+      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>-0.06282672747192664</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>-0.06741970375786777</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>-0.1262973638890311</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0.09341741893878452</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0.1510395202917948</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>-0.1034054819434311</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0.1557049962909995</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>0.4612172882401871</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>-0.1262973638890311</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0.04525875817249214</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>-0.1930637150180545</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>0.1532416716463302</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>-0.01906855625568105</v>
+      </c>
+      <c r="Y9" s="2" t="n">
+        <v>-0.05321604206871389</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.1057091888819022</v>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>-0.1437314915609249</v>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>-0.05253402809101404</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>-0.05717744768937194</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>-0.1821196302820544</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0.1004707929781817</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>0.251473119098452</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>-0.1821196302820544</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>0.05424292767282157</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>0.8123043424326933</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>-0.1821196302820544</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0.1584407781247144</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>-0.1056875720363117</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>0.536464778910649</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y10" s="2" t="n">
+        <v>-0.04281779134676389</v>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>0.008636370165942209</v>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v>-0.05101358927225752</v>
+      </c>
+      <c r="AB10" s="2" t="n">
+        <v>-0.007668307595080304</v>
+      </c>
+      <c r="AC10" s="2" t="n">
+        <v>-0.03624212783007885</v>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v>0.02964833913176146</v>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8827,24 +9960,22 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>156</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>373</v>
-      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="J2" s="2" t="n">
-        <v>0.496398891966759</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -8875,20 +10006,20 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-131</v>
+        <v>155</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>523</v>
+        <v>373</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.7274709302325582</v>
+        <v>0.4963948973932335</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -8921,20 +10052,24 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="n">
+        <v>-131</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>523</v>
+      </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>0.7274709302325582</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -8970,16 +10105,14 @@
         <v>0</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
@@ -9009,24 +10142,22 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>-442</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-174</v>
-      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="J6" s="2" t="n">
-        <v>0.2787524366471735</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -9057,21 +10188,23 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-114</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+        <v>-442</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-174</v>
+      </c>
       <c r="G7" t="n">
-        <v>114</v>
+        <v>442</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>0.2787524366471735</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -9088,37 +10221,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>156</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>18</v>
-      </c>
+        <v>-114</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="2" t="n">
-        <v>0.08476454293628809</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -9145,27 +10276,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>81</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="J9" s="2" t="n">
-        <v>0.3350290697674418</v>
+        <v>0.4777777777777778</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -9192,14 +10321,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -9209,10 +10338,10 @@
       </c>
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="2" t="n">
-        <v>0.5517241379310345</v>
+        <v>0.08485856905158069</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -9239,27 +10368,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-10</v>
+        <v>39</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="2" t="n">
-        <v>0.7622950819672131</v>
+        <v>0.3350290697674418</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -9286,27 +10415,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-21</v>
+        <v>31</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="2" t="n">
-        <v>0.4892787524366471</v>
+        <v>0.547945205479452</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -9333,27 +10462,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>9</v>
+        <v>-10</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="2" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -9370,37 +10499,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-35</v>
+        <v>-21</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="G14" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="2" t="n">
-        <v>0.3634349030470914</v>
+        <v>0.4892787524366471</v>
       </c>
       <c r="K14" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -9417,24 +10546,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -9444,10 +10573,10 @@
       </c>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="2" t="n">
-        <v>0.3960755813953488</v>
+        <v>0.4719101123595505</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -9474,27 +10603,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>30</v>
+        <v>-52</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>27</v>
+        <v>317</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
       </c>
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="2" t="n">
-        <v>0.4206896551724138</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -9521,27 +10650,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>9</v>
+        <v>-36</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="2" t="n">
-        <v>0.8770491803278688</v>
+        <v>0.3632834165280089</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -9568,27 +10697,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-21</v>
+        <v>39</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="G18" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>0.52046783625731</v>
+        <v>0.3960755813953488</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -9615,14 +10744,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -9632,7 +10761,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="2" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K19" t="n">
         <v>2</v>
@@ -9641,6 +10770,147 @@
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
+        <v>0.8492063492063492</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="G21" t="n">
+        <v>21</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
+        <v>0.52046783625731</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
+        <v>0.4719101123595505</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
